--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="55.00000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="5.5"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6 - 0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="47.300000000000004"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="55.00000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -274,7 +274,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>13:45 EDT</t>
+          <t>12:30 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -294,7 +294,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Met Oval Field - Met Oval Field </t>
+          <t>Red Hook Field #5 - Field 5 11v11</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 0</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2013-14-boys-u13-gray.xlsx
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 2</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
